--- a/Paper1/data/Table2_morans_i.xlsx
+++ b/Paper1/data/Table2_morans_i.xlsx
@@ -477,13 +477,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.0149</v>
+        <v>0.0009</v>
       </c>
       <c r="E2" t="n">
-        <v>0.803</v>
+        <v>1.536</v>
       </c>
       <c r="F2" t="n">
-        <v>0.204</v>
+        <v>0.073</v>
       </c>
     </row>
     <row r="3">
@@ -503,13 +503,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.0296</v>
+        <v>0.0891</v>
       </c>
       <c r="E3" t="n">
-        <v>0.773</v>
+        <v>1.643</v>
       </c>
       <c r="F3" t="n">
-        <v>0.214</v>
+        <v>0.058</v>
       </c>
     </row>
     <row r="4">
@@ -529,13 +529,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.0384</v>
+        <v>-0.0289</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.394</v>
+        <v>0.259</v>
       </c>
       <c r="F4" t="n">
-        <v>0.388</v>
+        <v>0.346</v>
       </c>
     </row>
     <row r="5">
@@ -555,13 +555,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.0516</v>
+        <v>-0.0076</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.34</v>
+        <v>0.494</v>
       </c>
       <c r="F5" t="n">
-        <v>0.39</v>
+        <v>0.278</v>
       </c>
     </row>
     <row r="6">
@@ -581,13 +581,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.06950000000000001</v>
+        <v>-0.015</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.41</v>
+        <v>0.25</v>
       </c>
       <c r="F6" t="n">
-        <v>0.363</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="7">
@@ -607,13 +607,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.1021</v>
+        <v>-0.0646</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.327</v>
       </c>
       <c r="F7" t="n">
-        <v>0.263</v>
+        <v>0.408</v>
       </c>
     </row>
     <row r="8">
@@ -633,13 +633,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.0508</v>
+        <v>-0.0178</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.244</v>
+        <v>0.267</v>
       </c>
       <c r="F8" t="n">
-        <v>0.432</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="9">
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.0634</v>
+        <v>-0.03</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.433</v>
+        <v>0.041</v>
       </c>
       <c r="F9" t="n">
-        <v>0.357</v>
+        <v>0.456</v>
       </c>
     </row>
   </sheetData>

--- a/Paper1/data/Table2_morans_i.xlsx
+++ b/Paper1/data/Table2_morans_i.xlsx
@@ -477,13 +477,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.0009</v>
+        <v>-0.0149</v>
       </c>
       <c r="E2" t="n">
-        <v>1.536</v>
+        <v>0.775</v>
       </c>
       <c r="F2" t="n">
-        <v>0.073</v>
+        <v>0.211</v>
       </c>
     </row>
     <row r="3">
@@ -503,13 +503,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.0891</v>
+        <v>0.0296</v>
       </c>
       <c r="E3" t="n">
-        <v>1.643</v>
+        <v>0.854</v>
       </c>
       <c r="F3" t="n">
-        <v>0.058</v>
+        <v>0.203</v>
       </c>
     </row>
     <row r="4">
@@ -529,13 +529,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.0289</v>
+        <v>-0.0384</v>
       </c>
       <c r="E4" t="n">
-        <v>0.259</v>
+        <v>-0.393</v>
       </c>
       <c r="F4" t="n">
-        <v>0.346</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="5">
@@ -555,13 +555,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.0076</v>
+        <v>-0.0516</v>
       </c>
       <c r="E5" t="n">
-        <v>0.494</v>
+        <v>-0.325</v>
       </c>
       <c r="F5" t="n">
-        <v>0.278</v>
+        <v>0.377</v>
       </c>
     </row>
     <row r="6">
@@ -581,13 +581,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.015</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>0.25</v>
+        <v>-0.372</v>
       </c>
       <c r="F6" t="n">
-        <v>0.375</v>
+        <v>0.386</v>
       </c>
     </row>
     <row r="7">
@@ -607,13 +607,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.0646</v>
+        <v>-0.1021</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.327</v>
+        <v>-0.745</v>
       </c>
       <c r="F7" t="n">
-        <v>0.408</v>
+        <v>0.239</v>
       </c>
     </row>
     <row r="8">
@@ -633,13 +633,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.0178</v>
+        <v>-0.0508</v>
       </c>
       <c r="E8" t="n">
-        <v>0.267</v>
+        <v>-0.261</v>
       </c>
       <c r="F8" t="n">
-        <v>0.375</v>
+        <v>0.445</v>
       </c>
     </row>
     <row r="9">
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.03</v>
+        <v>-0.0634</v>
       </c>
       <c r="E9" t="n">
-        <v>0.041</v>
+        <v>-0.48</v>
       </c>
       <c r="F9" t="n">
-        <v>0.456</v>
+        <v>0.335</v>
       </c>
     </row>
   </sheetData>
